--- a/Data/IND/FABLE.xlsx
+++ b/Data/IND/FABLE.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clara DOUZAL\Documents\Github Desktop\DownscalingFABLE\Data\IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB095AB-18A7-41FA-8FAD-1C5083F8677E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7FB42B-4DEA-49DE-855B-4F741C3C9083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10461ED0-0A96-44CE-86CA-319C52581F24}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{10461ED0-0A96-44CE-86CA-319C52581F24}"/>
   </bookViews>
   <sheets>
     <sheet name="CurrentTrends" sheetId="1" r:id="rId1"/>
-    <sheet name="NationalCommitments" sheetId="2" r:id="rId2"/>
-    <sheet name="GlobalSustainability" sheetId="3" r:id="rId3"/>
+    <sheet name="Baseline" sheetId="4" r:id="rId2"/>
+    <sheet name="NationalCommitments" sheetId="2" r:id="rId3"/>
+    <sheet name="GlobalSustainability" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="24">
   <si>
     <t>LandCoverInit</t>
   </si>
@@ -83,6 +84,33 @@
   </si>
   <si>
     <t>NewForest</t>
+  </si>
+  <si>
+    <t>LandCover</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>cropland</t>
+  </si>
+  <si>
+    <t>pasture</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>newforest</t>
+  </si>
+  <si>
+    <t>forest</t>
+  </si>
+  <si>
+    <t>otherland</t>
+  </si>
+  <si>
+    <t>not relevant</t>
   </si>
 </sst>
 </file>
@@ -2273,6 +2301,80 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22657D6F-409E-453B-9A78-12BCC2059112}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>169413</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>10262.754646368547</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>2227.6714938742321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>67591</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <v>47824.573859757249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0090468E-82DD-4BA2-B54A-6FCCDCE9F12F}">
   <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -4051,7 +4153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7301B5-1FC0-446C-8B04-03B45EA22A45}">
   <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/Data/IND/FABLE.xlsx
+++ b/Data/IND/FABLE.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clara DOUZAL\Documents\Github Desktop\DownscalingFABLE\Data\IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7FB42B-4DEA-49DE-855B-4F741C3C9083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FF71AB-C2D6-4818-8716-BA234B821951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{10461ED0-0A96-44CE-86CA-319C52581F24}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{10461ED0-0A96-44CE-86CA-319C52581F24}"/>
   </bookViews>
   <sheets>
     <sheet name="CurrentTrends" sheetId="1" r:id="rId1"/>
     <sheet name="Baseline" sheetId="4" r:id="rId2"/>
-    <sheet name="NationalCommitments" sheetId="2" r:id="rId3"/>
-    <sheet name="GlobalSustainability" sheetId="3" r:id="rId4"/>
+    <sheet name="MegaOptimist" sheetId="5" r:id="rId3"/>
+    <sheet name="NationalCommitments" sheetId="2" r:id="rId4"/>
+    <sheet name="GlobalSustainability" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="24">
   <si>
     <t>LandCoverInit</t>
   </si>
@@ -2375,6 +2376,1785 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{271C8962-1EC8-4738-9A46-52374F573C44}">
+  <dimension ref="A1:I61"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>2000</v>
+      </c>
+      <c r="C2">
+        <v>2005</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>2005</v>
+      </c>
+      <c r="C3">
+        <v>2010</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>2010</v>
+      </c>
+      <c r="C4">
+        <v>2015</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>2015</v>
+      </c>
+      <c r="C5">
+        <v>2020</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>2020</v>
+      </c>
+      <c r="C6">
+        <v>2025</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>2025</v>
+      </c>
+      <c r="C7">
+        <v>2030</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>2030</v>
+      </c>
+      <c r="C8">
+        <v>2035</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>2035</v>
+      </c>
+      <c r="C9">
+        <v>2040</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2040</v>
+      </c>
+      <c r="C10">
+        <v>2045</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>2045</v>
+      </c>
+      <c r="C11">
+        <v>2050</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>2000</v>
+      </c>
+      <c r="C12">
+        <v>2005</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>16.675678715636394</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>2005</v>
+      </c>
+      <c r="C13">
+        <v>2010</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>22.507289207844167</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>2010</v>
+      </c>
+      <c r="C14">
+        <v>2015</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>604.29560959624359</v>
+      </c>
+      <c r="G14">
+        <v>47.329816724530247</v>
+      </c>
+      <c r="H14">
+        <v>30.37825782830248</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>2015</v>
+      </c>
+      <c r="C15">
+        <v>2020</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>41.001763480303794</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>2020</v>
+      </c>
+      <c r="C16">
+        <v>2025</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>38.622713441222459</v>
+      </c>
+      <c r="I16">
+        <v>10611.02695361471</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>2025</v>
+      </c>
+      <c r="C17">
+        <v>2030</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>35.581277881810706</v>
+      </c>
+      <c r="I17">
+        <v>3537.0089845382372</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>2030</v>
+      </c>
+      <c r="C18">
+        <v>2035</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>31.316148278448225</v>
+      </c>
+      <c r="I18">
+        <v>3537.0089845382445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>2035</v>
+      </c>
+      <c r="C19">
+        <v>2040</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>28.161374760128808</v>
+      </c>
+      <c r="I19">
+        <v>3537.0089845382281</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>2040</v>
+      </c>
+      <c r="C20">
+        <v>2045</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>24.501332890633591</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2045</v>
+      </c>
+      <c r="C21">
+        <v>2050</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>21.316931163814104</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>2000</v>
+      </c>
+      <c r="C22">
+        <v>2005</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>222.54049798109918</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>233.45950201890932</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2005</v>
+      </c>
+      <c r="C23">
+        <v>2010</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>124.89795109018451</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>315.10204890981811</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>2010</v>
+      </c>
+      <c r="C24">
+        <v>2015</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>425.29560959623461</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>2015</v>
+      </c>
+      <c r="C25">
+        <v>2020</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>791.02731127574225</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>574.02468872425334</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>2020</v>
+      </c>
+      <c r="C26">
+        <v>2025</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>540.71798817711476</v>
+      </c>
+      <c r="I26">
+        <v>37028.572921019644</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>2025</v>
+      </c>
+      <c r="C27">
+        <v>2030</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>498.13789034535012</v>
+      </c>
+      <c r="I27">
+        <v>12342.857640339884</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>2030</v>
+      </c>
+      <c r="C28">
+        <v>2035</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>438.42607589827543</v>
+      </c>
+      <c r="I28">
+        <v>12342.857640339906</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>2035</v>
+      </c>
+      <c r="C29">
+        <v>2040</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>394.2592466418036</v>
+      </c>
+      <c r="I29">
+        <v>12342.857640339855</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>2040</v>
+      </c>
+      <c r="C30">
+        <v>2045</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>343.01866046887056</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>2045</v>
+      </c>
+      <c r="C31">
+        <v>2050</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>298.43703629339706</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32">
+        <v>2000</v>
+      </c>
+      <c r="C32">
+        <v>2005</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>329.37608752353663</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>66.702714862545534</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33">
+        <v>2005</v>
+      </c>
+      <c r="C33">
+        <v>2010</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>22.7614614316808</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>90.029156831376611</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34">
+        <v>2010</v>
+      </c>
+      <c r="C34">
+        <v>2015</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>121.51303131320991</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35">
+        <v>2015</v>
+      </c>
+      <c r="C35">
+        <v>2020</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>164.00705392121526</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36">
+        <v>2020</v>
+      </c>
+      <c r="C36">
+        <v>2025</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>154.49085376488995</v>
+      </c>
+      <c r="I36">
+        <v>2360.4001253656497</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37">
+        <v>2025</v>
+      </c>
+      <c r="C37">
+        <v>2030</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>142.32511152724291</v>
+      </c>
+      <c r="I37">
+        <v>786.80004178855006</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38">
+        <v>2030</v>
+      </c>
+      <c r="C38">
+        <v>2035</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>125.264593113793</v>
+      </c>
+      <c r="I38">
+        <v>786.80004178855188</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39">
+        <v>2035</v>
+      </c>
+      <c r="C39">
+        <v>2040</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>112.64549904051532</v>
+      </c>
+      <c r="I39">
+        <v>786.80004178854779</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40">
+        <v>2040</v>
+      </c>
+      <c r="C40">
+        <v>2045</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>98.005331562534451</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41">
+        <v>2045</v>
+      </c>
+      <c r="C41">
+        <v>2050</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>85.267724655256316</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42">
+        <v>2000</v>
+      </c>
+      <c r="C42">
+        <v>2005</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43">
+        <v>2005</v>
+      </c>
+      <c r="C43">
+        <v>2010</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44">
+        <v>2010</v>
+      </c>
+      <c r="C44">
+        <v>2015</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45">
+        <v>2015</v>
+      </c>
+      <c r="C45">
+        <v>2020</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46">
+        <v>2020</v>
+      </c>
+      <c r="C46">
+        <v>2025</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47">
+        <v>2025</v>
+      </c>
+      <c r="C47">
+        <v>2030</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48">
+        <v>2030</v>
+      </c>
+      <c r="C48">
+        <v>2035</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49">
+        <v>2035</v>
+      </c>
+      <c r="C49">
+        <v>2040</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50">
+        <v>2040</v>
+      </c>
+      <c r="C50">
+        <v>2045</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51">
+        <v>2045</v>
+      </c>
+      <c r="C51">
+        <v>2050</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52">
+        <v>2000</v>
+      </c>
+      <c r="C52">
+        <v>2005</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53">
+        <v>2005</v>
+      </c>
+      <c r="C53">
+        <v>2010</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54">
+        <v>2010</v>
+      </c>
+      <c r="C54">
+        <v>2015</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55">
+        <v>2015</v>
+      </c>
+      <c r="C55">
+        <v>2020</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56">
+        <v>2020</v>
+      </c>
+      <c r="C56">
+        <v>2025</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57">
+        <v>2025</v>
+      </c>
+      <c r="C57">
+        <v>2030</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58">
+        <v>2030</v>
+      </c>
+      <c r="C58">
+        <v>2035</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59">
+        <v>2035</v>
+      </c>
+      <c r="C59">
+        <v>2040</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60">
+        <v>2040</v>
+      </c>
+      <c r="C60">
+        <v>2045</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61">
+        <v>2045</v>
+      </c>
+      <c r="C61">
+        <v>2050</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0090468E-82DD-4BA2-B54A-6FCCDCE9F12F}">
   <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -4153,7 +5933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7301B5-1FC0-446C-8B04-03B45EA22A45}">
   <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
